--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕНЕРДЖИ ПЛЮС ЕООД/ЕНЕРДЖИ ПЛЮС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕНЕРДЖИ ПЛЮС ЕООД/ЕНЕРДЖИ ПЛЮС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,13 +61,22 @@
     <t>2026-05-11</t>
   </si>
   <si>
+    <t>1902 София, О5 Малинова Долина</t>
+  </si>
+  <si>
     <t>78970110027720217</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>16:30</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
+    <t>3231727457 3231727457</t>
   </si>
   <si>
     <t>Общи литри по продукт / ЕНЕРДЖИ ПЛЮС ЕООД</t>
@@ -488,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -497,16 +509,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -546,51 +559,57 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1902</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
       </c>
       <c r="C2">
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>47.68</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2">
         <v>1.47</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>70.09</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.55</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>73.90000000000001</v>
       </c>
-      <c r="K2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>168989</v>
+      <c r="N2" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14">
       <c r="A5" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -598,29 +617,29 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:14">
       <c r="A7" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" s="6">
         <v>47.68</v>
@@ -638,9 +657,9 @@
         <v>73.90000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:14">
       <c r="A8" s="8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B8" s="9">
         <v>47.68</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕНЕРДЖИ ПЛЮС ЕООД/ЕНЕРДЖИ ПЛЮС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕНЕРДЖИ ПЛЮС ЕООД/ЕНЕРДЖИ ПЛЮС ЕООД.xlsx
@@ -130,7 +130,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -140,12 +140,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -195,17 +189,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕНЕРДЖИ ПЛЮС ЕООД/ЕНЕРДЖИ ПЛЮС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕНЕРДЖИ ПЛЮС ЕООД/ЕНЕРДЖИ ПЛЮС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,34 +46,19 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>1902 София, О5 Малинова Долина</t>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>София Черни връх</t>
   </si>
   <si>
     <t>78970110027720217</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>16:30:00</t>
-  </si>
-  <si>
-    <t>3231727457 3231727457</t>
+    <t>EKO RACING 100</t>
   </si>
   <si>
     <t>Общи литри по продукт / ЕНЕРДЖИ ПЛЮС ЕООД</t>
@@ -494,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -503,17 +485,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -547,63 +526,45 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="B2" t="s">
         <v>12</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
       </c>
       <c r="C2">
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>47.68</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
+        <v>59.75</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.81</v>
       </c>
       <c r="H2">
-        <v>1.47</v>
+        <v>108.15</v>
       </c>
       <c r="I2" s="1">
-        <v>70.09</v>
+        <v>1.81</v>
       </c>
       <c r="J2">
-        <v>1.55</v>
-      </c>
-      <c r="K2" s="1">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2">
+        <v>108.15</v>
+      </c>
+      <c r="K2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>20</v>
-      </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:11">
       <c r="A5" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -611,62 +572,62 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:11">
       <c r="A6" s="4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:11">
       <c r="A7" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B7" s="6">
-        <v>47.68</v>
+        <v>59.75</v>
       </c>
       <c r="C7" s="6">
         <v>1</v>
       </c>
       <c r="D7" s="7">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="E7" s="6">
-        <v>70.09</v>
+        <v>108.15</v>
       </c>
       <c r="F7" s="6">
-        <v>73.90000000000001</v>
+        <v>108.15</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:11">
       <c r="A8" s="8" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B8" s="9">
-        <v>47.68</v>
+        <v>59.75</v>
       </c>
       <c r="C8" s="9">
         <v>1</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="9">
-        <v>70.09</v>
+        <v>108.15</v>
       </c>
       <c r="F8" s="9">
-        <v>73.90000000000001</v>
+        <v>108.15</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕНЕРДЖИ ПЛЮС ЕООД/ЕНЕРДЖИ ПЛЮС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕНЕРДЖИ ПЛЮС ЕООД/ЕНЕРДЖИ ПЛЮС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,10 +52,16 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-08</t>
   </si>
   <si>
-    <t>София Черни връх</t>
+    <t>1117 София Черни Връх</t>
   </si>
   <si>
     <t>78970110027720217</t>
@@ -61,7 +70,13 @@
     <t>EKO RACING 100</t>
   </si>
   <si>
-    <t>2026-06-08 13:12:34</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>13:07:00</t>
+  </si>
+  <si>
+    <t>3233022819 3233022819</t>
   </si>
   <si>
     <t>Общи литри по продукт / ЕНЕРДЖИ ПЛЮС ЕООД</t>
@@ -479,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -488,14 +503,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -529,45 +547,63 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>59.75</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2">
         <v>1.81</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>108.15</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.81</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>108.15</v>
       </c>
-      <c r="K2" t="s">
-        <v>15</v>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:14">
       <c r="A5" s="3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -575,29 +611,29 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:14">
       <c r="A6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="5" t="s">
-        <v>14</v>
       </c>
       <c r="B7" s="6">
         <v>59.75</v>
@@ -615,9 +651,9 @@
         <v>108.15</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:14">
       <c r="A8" s="8" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B8" s="9">
         <v>59.75</v>
